--- a/fase2/Evidencias Proyecto/Evidencias de Documentacion/03_Sprint_Backlog/Sprint_07/DPAY3_Sprint_Backlog_S07.xlsx
+++ b/fase2/Evidencias Proyecto/Evidencias de Documentacion/03_Sprint_Backlog/Sprint_07/DPAY3_Sprint_Backlog_S07.xlsx
@@ -530,7 +530,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sprint Backlog — D-PAY 3.0 — Sprint 7 (Semanas 17 y 18, 30/11/2026 – 12/12/2026)</t>
+          <t>Sprint Backlog - D-PAY 3.0 - Sprint 7 (Semanas 17 y 18, 30/11/2026 – 12/12/2026)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -539,6 +539,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -832,6 +833,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
